--- a/data/personal_transactions.xlsx
+++ b/data/personal_transactions.xlsx
@@ -5,21 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nobod\Desktop\DataPractice\archive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nobod\Desktop\DataPractice\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C949838F-C30F-44D7-B045-3F7FC298A484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703B9859-6776-4B8A-884C-278FCCDE2F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId3"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3255" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3230" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -329,15 +325,6 @@
   <si>
     <t>Silver Card</t>
   </si>
-  <si>
-    <t>Etiquetas de fila</t>
-  </si>
-  <si>
-    <t>Total general</t>
-  </si>
-  <si>
-    <t>Suma de Amount</t>
-  </si>
 </sst>
 </file>
 
@@ -398,17 +385,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,7753 +406,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Nobody Unknown" refreshedDate="46173.765646412037" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="806" xr:uid="{1F87C1D7-5CA0-47B7-8F9F-F1452D1671F9}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:F807" sheet="Sheet1"/>
-  </cacheSource>
-  <cacheFields count="9">
-    <cacheField name="Date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2018-01-01T00:00:00" maxDate="2019-10-01T00:00:00" count="432">
-        <d v="2018-01-01T00:00:00"/>
-        <d v="2018-01-02T00:00:00"/>
-        <d v="2018-01-03T00:00:00"/>
-        <d v="2018-01-04T00:00:00"/>
-        <d v="2018-01-05T00:00:00"/>
-        <d v="2018-01-06T00:00:00"/>
-        <d v="2018-01-08T00:00:00"/>
-        <d v="2018-01-09T00:00:00"/>
-        <d v="2018-01-10T00:00:00"/>
-        <d v="2018-01-11T00:00:00"/>
-        <d v="2018-01-12T00:00:00"/>
-        <d v="2018-01-13T00:00:00"/>
-        <d v="2018-01-15T00:00:00"/>
-        <d v="2018-01-16T00:00:00"/>
-        <d v="2018-01-19T00:00:00"/>
-        <d v="2018-01-20T00:00:00"/>
-        <d v="2018-01-22T00:00:00"/>
-        <d v="2018-01-23T00:00:00"/>
-        <d v="2018-01-24T00:00:00"/>
-        <d v="2018-01-25T00:00:00"/>
-        <d v="2018-01-29T00:00:00"/>
-        <d v="2018-02-01T00:00:00"/>
-        <d v="2018-02-02T00:00:00"/>
-        <d v="2018-02-03T00:00:00"/>
-        <d v="2018-02-04T00:00:00"/>
-        <d v="2018-02-05T00:00:00"/>
-        <d v="2018-02-06T00:00:00"/>
-        <d v="2018-02-07T00:00:00"/>
-        <d v="2018-02-09T00:00:00"/>
-        <d v="2018-02-10T00:00:00"/>
-        <d v="2018-02-11T00:00:00"/>
-        <d v="2018-02-12T00:00:00"/>
-        <d v="2018-02-14T00:00:00"/>
-        <d v="2018-02-15T00:00:00"/>
-        <d v="2018-02-16T00:00:00"/>
-        <d v="2018-02-20T00:00:00"/>
-        <d v="2018-02-21T00:00:00"/>
-        <d v="2018-02-22T00:00:00"/>
-        <d v="2018-02-26T00:00:00"/>
-        <d v="2018-02-27T00:00:00"/>
-        <d v="2018-03-01T00:00:00"/>
-        <d v="2018-03-02T00:00:00"/>
-        <d v="2018-03-03T00:00:00"/>
-        <d v="2018-03-04T00:00:00"/>
-        <d v="2018-03-05T00:00:00"/>
-        <d v="2018-03-07T00:00:00"/>
-        <d v="2018-03-08T00:00:00"/>
-        <d v="2018-03-09T00:00:00"/>
-        <d v="2018-03-12T00:00:00"/>
-        <d v="2018-03-13T00:00:00"/>
-        <d v="2018-03-14T00:00:00"/>
-        <d v="2018-03-15T00:00:00"/>
-        <d v="2018-03-16T00:00:00"/>
-        <d v="2018-03-17T00:00:00"/>
-        <d v="2018-03-19T00:00:00"/>
-        <d v="2018-03-20T00:00:00"/>
-        <d v="2018-03-22T00:00:00"/>
-        <d v="2018-03-23T00:00:00"/>
-        <d v="2018-03-26T00:00:00"/>
-        <d v="2018-03-28T00:00:00"/>
-        <d v="2018-03-29T00:00:00"/>
-        <d v="2018-03-30T00:00:00"/>
-        <d v="2018-03-31T00:00:00"/>
-        <d v="2018-04-01T00:00:00"/>
-        <d v="2018-04-02T00:00:00"/>
-        <d v="2018-04-03T00:00:00"/>
-        <d v="2018-04-04T00:00:00"/>
-        <d v="2018-04-06T00:00:00"/>
-        <d v="2018-04-08T00:00:00"/>
-        <d v="2018-04-09T00:00:00"/>
-        <d v="2018-04-11T00:00:00"/>
-        <d v="2018-04-12T00:00:00"/>
-        <d v="2018-04-13T00:00:00"/>
-        <d v="2018-04-14T00:00:00"/>
-        <d v="2018-04-16T00:00:00"/>
-        <d v="2018-04-18T00:00:00"/>
-        <d v="2018-04-20T00:00:00"/>
-        <d v="2018-04-21T00:00:00"/>
-        <d v="2018-04-22T00:00:00"/>
-        <d v="2018-04-23T00:00:00"/>
-        <d v="2018-04-24T00:00:00"/>
-        <d v="2018-04-25T00:00:00"/>
-        <d v="2018-04-26T00:00:00"/>
-        <d v="2018-04-27T00:00:00"/>
-        <d v="2018-04-28T00:00:00"/>
-        <d v="2018-04-29T00:00:00"/>
-        <d v="2018-04-30T00:00:00"/>
-        <d v="2018-05-01T00:00:00"/>
-        <d v="2018-05-02T00:00:00"/>
-        <d v="2018-05-03T00:00:00"/>
-        <d v="2018-05-04T00:00:00"/>
-        <d v="2018-05-05T00:00:00"/>
-        <d v="2018-05-06T00:00:00"/>
-        <d v="2018-05-09T00:00:00"/>
-        <d v="2018-05-10T00:00:00"/>
-        <d v="2018-05-11T00:00:00"/>
-        <d v="2018-05-12T00:00:00"/>
-        <d v="2018-05-14T00:00:00"/>
-        <d v="2018-05-15T00:00:00"/>
-        <d v="2018-05-17T00:00:00"/>
-        <d v="2018-05-18T00:00:00"/>
-        <d v="2018-05-19T00:00:00"/>
-        <d v="2018-05-21T00:00:00"/>
-        <d v="2018-05-22T00:00:00"/>
-        <d v="2018-05-24T00:00:00"/>
-        <d v="2018-05-25T00:00:00"/>
-        <d v="2018-05-28T00:00:00"/>
-        <d v="2018-05-29T00:00:00"/>
-        <d v="2018-06-01T00:00:00"/>
-        <d v="2018-06-02T00:00:00"/>
-        <d v="2018-06-03T00:00:00"/>
-        <d v="2018-06-04T00:00:00"/>
-        <d v="2018-06-06T00:00:00"/>
-        <d v="2018-06-08T00:00:00"/>
-        <d v="2018-06-09T00:00:00"/>
-        <d v="2018-06-10T00:00:00"/>
-        <d v="2018-06-12T00:00:00"/>
-        <d v="2018-06-14T00:00:00"/>
-        <d v="2018-06-15T00:00:00"/>
-        <d v="2018-06-16T00:00:00"/>
-        <d v="2018-06-18T00:00:00"/>
-        <d v="2018-06-19T00:00:00"/>
-        <d v="2018-06-20T00:00:00"/>
-        <d v="2018-06-21T00:00:00"/>
-        <d v="2018-06-22T00:00:00"/>
-        <d v="2018-06-23T00:00:00"/>
-        <d v="2018-06-25T00:00:00"/>
-        <d v="2018-06-26T00:00:00"/>
-        <d v="2018-06-27T00:00:00"/>
-        <d v="2018-06-28T00:00:00"/>
-        <d v="2018-07-01T00:00:00"/>
-        <d v="2018-07-02T00:00:00"/>
-        <d v="2018-07-04T00:00:00"/>
-        <d v="2018-07-05T00:00:00"/>
-        <d v="2018-07-06T00:00:00"/>
-        <d v="2018-07-08T00:00:00"/>
-        <d v="2018-07-09T00:00:00"/>
-        <d v="2018-07-10T00:00:00"/>
-        <d v="2018-07-11T00:00:00"/>
-        <d v="2018-07-14T00:00:00"/>
-        <d v="2018-07-15T00:00:00"/>
-        <d v="2018-07-17T00:00:00"/>
-        <d v="2018-07-18T00:00:00"/>
-        <d v="2018-07-20T00:00:00"/>
-        <d v="2018-07-21T00:00:00"/>
-        <d v="2018-07-23T00:00:00"/>
-        <d v="2018-07-24T00:00:00"/>
-        <d v="2018-07-25T00:00:00"/>
-        <d v="2018-07-26T00:00:00"/>
-        <d v="2018-07-28T00:00:00"/>
-        <d v="2018-07-30T00:00:00"/>
-        <d v="2018-07-31T00:00:00"/>
-        <d v="2018-08-01T00:00:00"/>
-        <d v="2018-08-02T00:00:00"/>
-        <d v="2018-08-03T00:00:00"/>
-        <d v="2018-08-04T00:00:00"/>
-        <d v="2018-08-06T00:00:00"/>
-        <d v="2018-08-09T00:00:00"/>
-        <d v="2018-08-10T00:00:00"/>
-        <d v="2018-08-11T00:00:00"/>
-        <d v="2018-08-15T00:00:00"/>
-        <d v="2018-08-16T00:00:00"/>
-        <d v="2018-08-17T00:00:00"/>
-        <d v="2018-08-18T00:00:00"/>
-        <d v="2018-08-20T00:00:00"/>
-        <d v="2018-08-21T00:00:00"/>
-        <d v="2018-08-22T00:00:00"/>
-        <d v="2018-08-24T00:00:00"/>
-        <d v="2018-08-27T00:00:00"/>
-        <d v="2018-08-30T00:00:00"/>
-        <d v="2018-08-31T00:00:00"/>
-        <d v="2018-09-01T00:00:00"/>
-        <d v="2018-09-02T00:00:00"/>
-        <d v="2018-09-04T00:00:00"/>
-        <d v="2018-09-07T00:00:00"/>
-        <d v="2018-09-09T00:00:00"/>
-        <d v="2018-09-11T00:00:00"/>
-        <d v="2018-09-12T00:00:00"/>
-        <d v="2018-09-13T00:00:00"/>
-        <d v="2018-09-14T00:00:00"/>
-        <d v="2018-09-17T00:00:00"/>
-        <d v="2018-09-18T00:00:00"/>
-        <d v="2018-09-19T00:00:00"/>
-        <d v="2018-09-20T00:00:00"/>
-        <d v="2018-09-22T00:00:00"/>
-        <d v="2018-09-25T00:00:00"/>
-        <d v="2018-09-26T00:00:00"/>
-        <d v="2018-09-27T00:00:00"/>
-        <d v="2018-09-28T00:00:00"/>
-        <d v="2018-09-29T00:00:00"/>
-        <d v="2018-10-01T00:00:00"/>
-        <d v="2018-10-02T00:00:00"/>
-        <d v="2018-10-04T00:00:00"/>
-        <d v="2018-10-06T00:00:00"/>
-        <d v="2018-10-08T00:00:00"/>
-        <d v="2018-10-09T00:00:00"/>
-        <d v="2018-10-10T00:00:00"/>
-        <d v="2018-10-11T00:00:00"/>
-        <d v="2018-10-12T00:00:00"/>
-        <d v="2018-10-16T00:00:00"/>
-        <d v="2018-10-17T00:00:00"/>
-        <d v="2018-10-18T00:00:00"/>
-        <d v="2018-10-21T00:00:00"/>
-        <d v="2018-10-22T00:00:00"/>
-        <d v="2018-10-23T00:00:00"/>
-        <d v="2018-10-25T00:00:00"/>
-        <d v="2018-10-26T00:00:00"/>
-        <d v="2018-10-27T00:00:00"/>
-        <d v="2018-10-28T00:00:00"/>
-        <d v="2018-10-31T00:00:00"/>
-        <d v="2018-11-01T00:00:00"/>
-        <d v="2018-11-02T00:00:00"/>
-        <d v="2018-11-03T00:00:00"/>
-        <d v="2018-11-04T00:00:00"/>
-        <d v="2018-11-05T00:00:00"/>
-        <d v="2018-11-06T00:00:00"/>
-        <d v="2018-11-08T00:00:00"/>
-        <d v="2018-11-09T00:00:00"/>
-        <d v="2018-11-10T00:00:00"/>
-        <d v="2018-11-12T00:00:00"/>
-        <d v="2018-11-13T00:00:00"/>
-        <d v="2018-11-14T00:00:00"/>
-        <d v="2018-11-16T00:00:00"/>
-        <d v="2018-11-17T00:00:00"/>
-        <d v="2018-11-19T00:00:00"/>
-        <d v="2018-11-20T00:00:00"/>
-        <d v="2018-11-21T00:00:00"/>
-        <d v="2018-11-23T00:00:00"/>
-        <d v="2018-11-26T00:00:00"/>
-        <d v="2018-11-27T00:00:00"/>
-        <d v="2018-11-29T00:00:00"/>
-        <d v="2018-11-30T00:00:00"/>
-        <d v="2018-12-01T00:00:00"/>
-        <d v="2018-12-03T00:00:00"/>
-        <d v="2018-12-04T00:00:00"/>
-        <d v="2018-12-06T00:00:00"/>
-        <d v="2018-12-07T00:00:00"/>
-        <d v="2018-12-08T00:00:00"/>
-        <d v="2018-12-09T00:00:00"/>
-        <d v="2018-12-11T00:00:00"/>
-        <d v="2018-12-12T00:00:00"/>
-        <d v="2018-12-13T00:00:00"/>
-        <d v="2018-12-14T00:00:00"/>
-        <d v="2018-12-17T00:00:00"/>
-        <d v="2018-12-18T00:00:00"/>
-        <d v="2018-12-19T00:00:00"/>
-        <d v="2018-12-20T00:00:00"/>
-        <d v="2018-12-21T00:00:00"/>
-        <d v="2018-12-22T00:00:00"/>
-        <d v="2018-12-23T00:00:00"/>
-        <d v="2018-12-24T00:00:00"/>
-        <d v="2018-12-26T00:00:00"/>
-        <d v="2018-12-28T00:00:00"/>
-        <d v="2018-12-29T00:00:00"/>
-        <d v="2019-01-01T00:00:00"/>
-        <d v="2019-01-02T00:00:00"/>
-        <d v="2019-01-03T00:00:00"/>
-        <d v="2019-01-04T00:00:00"/>
-        <d v="2019-01-05T00:00:00"/>
-        <d v="2019-01-08T00:00:00"/>
-        <d v="2019-01-09T00:00:00"/>
-        <d v="2019-01-10T00:00:00"/>
-        <d v="2019-01-14T00:00:00"/>
-        <d v="2019-01-15T00:00:00"/>
-        <d v="2019-01-16T00:00:00"/>
-        <d v="2019-01-18T00:00:00"/>
-        <d v="2019-01-21T00:00:00"/>
-        <d v="2019-01-22T00:00:00"/>
-        <d v="2019-01-24T00:00:00"/>
-        <d v="2019-01-25T00:00:00"/>
-        <d v="2019-01-31T00:00:00"/>
-        <d v="2019-02-01T00:00:00"/>
-        <d v="2019-02-04T00:00:00"/>
-        <d v="2019-02-05T00:00:00"/>
-        <d v="2019-02-07T00:00:00"/>
-        <d v="2019-02-08T00:00:00"/>
-        <d v="2019-02-09T00:00:00"/>
-        <d v="2019-02-11T00:00:00"/>
-        <d v="2019-02-12T00:00:00"/>
-        <d v="2019-02-13T00:00:00"/>
-        <d v="2019-02-15T00:00:00"/>
-        <d v="2019-02-16T00:00:00"/>
-        <d v="2019-02-19T00:00:00"/>
-        <d v="2019-02-20T00:00:00"/>
-        <d v="2019-02-21T00:00:00"/>
-        <d v="2019-02-25T00:00:00"/>
-        <d v="2019-02-27T00:00:00"/>
-        <d v="2019-02-28T00:00:00"/>
-        <d v="2019-03-01T00:00:00"/>
-        <d v="2019-03-04T00:00:00"/>
-        <d v="2019-03-05T00:00:00"/>
-        <d v="2019-03-06T00:00:00"/>
-        <d v="2019-03-08T00:00:00"/>
-        <d v="2019-03-09T00:00:00"/>
-        <d v="2019-03-12T00:00:00"/>
-        <d v="2019-03-13T00:00:00"/>
-        <d v="2019-03-14T00:00:00"/>
-        <d v="2019-03-15T00:00:00"/>
-        <d v="2019-03-18T00:00:00"/>
-        <d v="2019-03-19T00:00:00"/>
-        <d v="2019-03-20T00:00:00"/>
-        <d v="2019-03-22T00:00:00"/>
-        <d v="2019-03-23T00:00:00"/>
-        <d v="2019-03-25T00:00:00"/>
-        <d v="2019-03-26T00:00:00"/>
-        <d v="2019-03-27T00:00:00"/>
-        <d v="2019-03-29T00:00:00"/>
-        <d v="2019-03-30T00:00:00"/>
-        <d v="2019-03-31T00:00:00"/>
-        <d v="2019-04-01T00:00:00"/>
-        <d v="2019-04-02T00:00:00"/>
-        <d v="2019-04-04T00:00:00"/>
-        <d v="2019-04-06T00:00:00"/>
-        <d v="2019-04-08T00:00:00"/>
-        <d v="2019-04-09T00:00:00"/>
-        <d v="2019-04-10T00:00:00"/>
-        <d v="2019-04-12T00:00:00"/>
-        <d v="2019-04-13T00:00:00"/>
-        <d v="2019-04-15T00:00:00"/>
-        <d v="2019-04-16T00:00:00"/>
-        <d v="2019-04-18T00:00:00"/>
-        <d v="2019-04-19T00:00:00"/>
-        <d v="2019-04-22T00:00:00"/>
-        <d v="2019-04-23T00:00:00"/>
-        <d v="2019-04-25T00:00:00"/>
-        <d v="2019-04-26T00:00:00"/>
-        <d v="2019-04-27T00:00:00"/>
-        <d v="2019-04-29T00:00:00"/>
-        <d v="2019-04-30T00:00:00"/>
-        <d v="2019-05-01T00:00:00"/>
-        <d v="2019-05-02T00:00:00"/>
-        <d v="2019-05-03T00:00:00"/>
-        <d v="2019-05-04T00:00:00"/>
-        <d v="2019-05-06T00:00:00"/>
-        <d v="2019-05-07T00:00:00"/>
-        <d v="2019-05-09T00:00:00"/>
-        <d v="2019-05-10T00:00:00"/>
-        <d v="2019-05-13T00:00:00"/>
-        <d v="2019-05-14T00:00:00"/>
-        <d v="2019-05-15T00:00:00"/>
-        <d v="2019-05-17T00:00:00"/>
-        <d v="2019-05-20T00:00:00"/>
-        <d v="2019-05-24T00:00:00"/>
-        <d v="2019-05-25T00:00:00"/>
-        <d v="2019-05-27T00:00:00"/>
-        <d v="2019-05-28T00:00:00"/>
-        <d v="2019-05-30T00:00:00"/>
-        <d v="2019-06-01T00:00:00"/>
-        <d v="2019-06-03T00:00:00"/>
-        <d v="2019-06-04T00:00:00"/>
-        <d v="2019-06-05T00:00:00"/>
-        <d v="2019-06-06T00:00:00"/>
-        <d v="2019-06-07T00:00:00"/>
-        <d v="2019-06-09T00:00:00"/>
-        <d v="2019-06-12T00:00:00"/>
-        <d v="2019-06-13T00:00:00"/>
-        <d v="2019-06-14T00:00:00"/>
-        <d v="2019-06-15T00:00:00"/>
-        <d v="2019-06-17T00:00:00"/>
-        <d v="2019-06-18T00:00:00"/>
-        <d v="2019-06-19T00:00:00"/>
-        <d v="2019-06-20T00:00:00"/>
-        <d v="2019-06-21T00:00:00"/>
-        <d v="2019-06-24T00:00:00"/>
-        <d v="2019-06-28T00:00:00"/>
-        <d v="2019-06-30T00:00:00"/>
-        <d v="2019-07-01T00:00:00"/>
-        <d v="2019-07-02T00:00:00"/>
-        <d v="2019-07-04T00:00:00"/>
-        <d v="2019-07-05T00:00:00"/>
-        <d v="2019-07-06T00:00:00"/>
-        <d v="2019-07-07T00:00:00"/>
-        <d v="2019-07-08T00:00:00"/>
-        <d v="2019-07-09T00:00:00"/>
-        <d v="2019-07-10T00:00:00"/>
-        <d v="2019-07-15T00:00:00"/>
-        <d v="2019-07-16T00:00:00"/>
-        <d v="2019-07-17T00:00:00"/>
-        <d v="2019-07-18T00:00:00"/>
-        <d v="2019-07-19T00:00:00"/>
-        <d v="2019-07-22T00:00:00"/>
-        <d v="2019-07-23T00:00:00"/>
-        <d v="2019-07-24T00:00:00"/>
-        <d v="2019-07-27T00:00:00"/>
-        <d v="2019-07-28T00:00:00"/>
-        <d v="2019-07-29T00:00:00"/>
-        <d v="2019-07-30T00:00:00"/>
-        <d v="2019-08-01T00:00:00"/>
-        <d v="2019-08-02T00:00:00"/>
-        <d v="2019-08-03T00:00:00"/>
-        <d v="2019-08-04T00:00:00"/>
-        <d v="2019-08-05T00:00:00"/>
-        <d v="2019-08-06T00:00:00"/>
-        <d v="2019-08-08T00:00:00"/>
-        <d v="2019-08-09T00:00:00"/>
-        <d v="2019-08-12T00:00:00"/>
-        <d v="2019-08-14T00:00:00"/>
-        <d v="2019-08-15T00:00:00"/>
-        <d v="2019-08-16T00:00:00"/>
-        <d v="2019-08-17T00:00:00"/>
-        <d v="2019-08-19T00:00:00"/>
-        <d v="2019-08-20T00:00:00"/>
-        <d v="2019-08-21T00:00:00"/>
-        <d v="2019-08-23T00:00:00"/>
-        <d v="2019-08-25T00:00:00"/>
-        <d v="2019-08-26T00:00:00"/>
-        <d v="2019-08-29T00:00:00"/>
-        <d v="2019-08-30T00:00:00"/>
-        <d v="2019-08-31T00:00:00"/>
-        <d v="2019-09-01T00:00:00"/>
-        <d v="2019-09-03T00:00:00"/>
-        <d v="2019-09-04T00:00:00"/>
-        <d v="2019-09-05T00:00:00"/>
-        <d v="2019-09-06T00:00:00"/>
-        <d v="2019-09-07T00:00:00"/>
-        <d v="2019-09-08T00:00:00"/>
-        <d v="2019-09-09T00:00:00"/>
-        <d v="2019-09-11T00:00:00"/>
-        <d v="2019-09-12T00:00:00"/>
-        <d v="2019-09-13T00:00:00"/>
-        <d v="2019-09-14T00:00:00"/>
-        <d v="2019-09-15T00:00:00"/>
-        <d v="2019-09-16T00:00:00"/>
-        <d v="2019-09-17T00:00:00"/>
-        <d v="2019-09-18T00:00:00"/>
-        <d v="2019-09-19T00:00:00"/>
-        <d v="2019-09-20T00:00:00"/>
-        <d v="2019-09-22T00:00:00"/>
-        <d v="2019-09-23T00:00:00"/>
-        <d v="2019-09-27T00:00:00"/>
-        <d v="2019-09-28T00:00:00"/>
-        <d v="2019-09-30T00:00:00"/>
-      </sharedItems>
-      <fieldGroup par="8"/>
-    </cacheField>
-    <cacheField name="Description" numFmtId="0">
-      <sharedItems count="65">
-        <s v="Amazon"/>
-        <s v="Mortgage Payment"/>
-        <s v="Thai Restaurant"/>
-        <s v="Credit Card Payment"/>
-        <s v="Netflix"/>
-        <s v="American Tavern"/>
-        <s v="Hardware Store"/>
-        <s v="Gas Company"/>
-        <s v="Spotify"/>
-        <s v="Phone Company"/>
-        <s v="Shell"/>
-        <s v="Grocery Store"/>
-        <s v="Biweekly Paycheck"/>
-        <s v="Pizza Place"/>
-        <s v="City Water Charges"/>
-        <s v="Power Company"/>
-        <s v="Starbucks"/>
-        <s v="Internet Service Provider"/>
-        <s v="Brunch Restaurant"/>
-        <s v="Japanese Restaurant"/>
-        <s v="Barbershop"/>
-        <s v="Bojangles"/>
-        <s v="Fancy Restaurant"/>
-        <s v="Brewing Company"/>
-        <s v="Mexican Restaurant"/>
-        <s v="Gas Station"/>
-        <s v="BBQ Restaurant"/>
-        <s v="BP"/>
-        <s v="Mediterranean Restaurant"/>
-        <s v="Steakhouse"/>
-        <s v="Belgian Restaurant"/>
-        <s v="Chili's"/>
-        <s v="Greek Restaurant"/>
-        <s v="Amazon Video"/>
-        <s v="Chevron"/>
-        <s v="Tiny Deli"/>
-        <s v="Irish Pub"/>
-        <s v="Blue Sky Market"/>
-        <s v="State Farm"/>
-        <s v="QuikTrip"/>
-        <s v="Mike's Construction Co."/>
-        <s v="Liquor Store"/>
-        <s v="Movie Theater"/>
-        <s v="Italian Restaurant"/>
-        <s v="Chick-Fil-A"/>
-        <s v="Go Mart"/>
-        <s v="Circle K"/>
-        <s v="Wendy's"/>
-        <s v="Irish Restaurant"/>
-        <s v="Conoco"/>
-        <s v="Valero"/>
-        <s v="Sushi Restaurant"/>
-        <s v="Exxon"/>
-        <s v="German Restaurant"/>
-        <s v="Seafood Restaurant"/>
-        <s v="Food Truck"/>
-        <s v="Latin Restaurant"/>
-        <s v="New York Deli"/>
-        <s v="Roadside Diner"/>
-        <s v="Bakery Place"/>
-        <s v="Best Buy"/>
-        <s v="Vietnamese Restaurant"/>
-        <s v="Target"/>
-        <s v="Hawaiian Grill"/>
-        <s v="Sheetz"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Amount" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.75" maxValue="9200"/>
-    </cacheField>
-    <cacheField name="Transaction Type" numFmtId="0">
-      <sharedItems count="2">
-        <s v="debit"/>
-        <s v="credit"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Category" numFmtId="0">
-      <sharedItems count="22">
-        <s v="Shopping"/>
-        <s v="Mortgage &amp; Rent"/>
-        <s v="Restaurants"/>
-        <s v="Credit Card Payment"/>
-        <s v="Movies &amp; Dvds"/>
-        <s v="Home Improvement"/>
-        <s v="Utilities"/>
-        <s v="Music"/>
-        <s v="Mobile Phone"/>
-        <s v="Gas &amp; Fuel"/>
-        <s v="Groceries"/>
-        <s v="Paycheck"/>
-        <s v="Fast Food"/>
-        <s v="Coffee Shops"/>
-        <s v="Internet"/>
-        <s v="Haircut"/>
-        <s v="Alcohol &amp; Bars"/>
-        <s v="Auto Insurance"/>
-        <s v="Entertainment"/>
-        <s v="Food &amp; Dining"/>
-        <s v="Television"/>
-        <s v="Electronics &amp; Software"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Account Name" numFmtId="0">
-      <sharedItems count="3">
-        <s v="Platinum Card"/>
-        <s v="Checking"/>
-        <s v="Silver Card"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Meses (Date)" numFmtId="0" databaseField="0">
-      <fieldGroup base="0">
-        <rangePr groupBy="months" startDate="2018-01-01T00:00:00" endDate="2019-10-01T00:00:00"/>
-        <groupItems count="14">
-          <s v="&lt;01/01/2018"/>
-          <s v="ene"/>
-          <s v="feb"/>
-          <s v="mar"/>
-          <s v="abr"/>
-          <s v="may"/>
-          <s v="jun"/>
-          <s v="jul"/>
-          <s v="ago"/>
-          <s v="sep"/>
-          <s v="oct"/>
-          <s v="nov"/>
-          <s v="dic"/>
-          <s v="&gt;01/10/2019"/>
-        </groupItems>
-      </fieldGroup>
-    </cacheField>
-    <cacheField name="Trimestres (Date)" numFmtId="0" databaseField="0">
-      <fieldGroup base="0">
-        <rangePr groupBy="quarters" startDate="2018-01-01T00:00:00" endDate="2019-10-01T00:00:00"/>
-        <groupItems count="6">
-          <s v="&lt;01/01/2018"/>
-          <s v="Trim.1"/>
-          <s v="Trim.2"/>
-          <s v="Trim.3"/>
-          <s v="Trim.4"/>
-          <s v="&gt;01/10/2019"/>
-        </groupItems>
-      </fieldGroup>
-    </cacheField>
-    <cacheField name="Años (Date)" numFmtId="0" databaseField="0">
-      <fieldGroup base="0">
-        <rangePr groupBy="years" startDate="2018-01-01T00:00:00" endDate="2019-10-01T00:00:00"/>
-        <groupItems count="4">
-          <s v="&lt;01/01/2018"/>
-          <s v="2018"/>
-          <s v="2019"/>
-          <s v="&gt;01/10/2019"/>
-        </groupItems>
-      </fieldGroup>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="806">
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="11.11"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1247.44"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="24.22"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="3"/>
-    <n v="2298.09"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="5"/>
-    <n v="25.85"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="6"/>
-    <n v="18.45"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="7"/>
-    <n v="45"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="6"/>
-    <n v="15.38"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="9"/>
-    <n v="89.46"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="10"/>
-    <n v="34.869999999999997"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="11"/>
-    <n v="43.54"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="13"/>
-    <n v="32.909999999999997"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="0"/>
-    <n v="39.049999999999997"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="11"/>
-    <n v="44.19"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="5"/>
-    <n v="64.11"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="13"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="13"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="14"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="15"/>
-    <x v="0"/>
-    <n v="50.21"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="16"/>
-    <x v="3"/>
-    <n v="554.99"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="16"/>
-    <x v="3"/>
-    <n v="309.81"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="16"/>
-    <x v="3"/>
-    <n v="554.99"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="16"/>
-    <x v="6"/>
-    <n v="17.38"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="17"/>
-    <x v="3"/>
-    <n v="309.81"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="18"/>
-    <x v="16"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="19"/>
-    <x v="17"/>
-    <n v="69.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="20"/>
-    <x v="10"/>
-    <n v="30.42"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="20"/>
-    <x v="2"/>
-    <n v="25"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="20"/>
-    <x v="18"/>
-    <n v="17.62"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="21"/>
-    <x v="11"/>
-    <n v="27.79"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="21"/>
-    <x v="0"/>
-    <n v="11.11"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="22"/>
-    <x v="1"/>
-    <n v="1247.44"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="22"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="23"/>
-    <x v="19"/>
-    <n v="57.02"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="24"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="25"/>
-    <x v="3"/>
-    <n v="145.13999999999999"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="26"/>
-    <x v="3"/>
-    <n v="154.13"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="27"/>
-    <x v="3"/>
-    <n v="154.13"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="27"/>
-    <x v="7"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="28"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="28"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="29"/>
-    <x v="21"/>
-    <n v="10.66"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="30"/>
-    <x v="22"/>
-    <n v="106.8"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="31"/>
-    <x v="10"/>
-    <n v="36.47"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="31"/>
-    <x v="9"/>
-    <n v="89.52"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="32"/>
-    <x v="23"/>
-    <n v="14"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="33"/>
-    <x v="5"/>
-    <n v="10"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="33"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="34"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="34"/>
-    <x v="18"/>
-    <n v="8"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="34"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="35"/>
-    <x v="11"/>
-    <n v="35.950000000000003"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="35"/>
-    <x v="24"/>
-    <n v="23.51"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="36"/>
-    <x v="16"/>
-    <n v="2"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="37"/>
-    <x v="16"/>
-    <n v="4"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <x v="3"/>
-    <n v="765.37"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <x v="3"/>
-    <n v="156.11000000000001"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <x v="3"/>
-    <n v="765.37"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <x v="5"/>
-    <n v="85.52"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <x v="25"/>
-    <n v="32.21"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="39"/>
-    <x v="3"/>
-    <n v="156.11000000000001"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="40"/>
-    <x v="11"/>
-    <n v="32.07"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="40"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="41"/>
-    <x v="1"/>
-    <n v="1247.44"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="41"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="42"/>
-    <x v="11"/>
-    <n v="23.74"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="43"/>
-    <x v="11"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="43"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="43"/>
-    <x v="26"/>
-    <n v="42.24"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="44"/>
-    <x v="16"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="44"/>
-    <x v="3"/>
-    <n v="761.59"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="44"/>
-    <x v="3"/>
-    <n v="761.59"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="45"/>
-    <x v="16"/>
-    <n v="3.5"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="46"/>
-    <x v="27"/>
-    <n v="34.9"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="46"/>
-    <x v="7"/>
-    <n v="52"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="47"/>
-    <x v="11"/>
-    <n v="20.72"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="47"/>
-    <x v="11"/>
-    <n v="5.09"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="47"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="48"/>
-    <x v="11"/>
-    <n v="19.350000000000001"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="48"/>
-    <x v="9"/>
-    <n v="89.52"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="49"/>
-    <x v="0"/>
-    <n v="45.75"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="50"/>
-    <x v="11"/>
-    <n v="22.5"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="50"/>
-    <x v="18"/>
-    <n v="8.49"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="51"/>
-    <x v="16"/>
-    <n v="3.5"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="51"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="52"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="53"/>
-    <x v="23"/>
-    <n v="19.5"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="53"/>
-    <x v="13"/>
-    <n v="23.34"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="54"/>
-    <x v="28"/>
-    <n v="36.479999999999997"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="54"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="55"/>
-    <x v="0"/>
-    <n v="14.97"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="56"/>
-    <x v="27"/>
-    <n v="30.55"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="57"/>
-    <x v="3"/>
-    <n v="559.91"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="57"/>
-    <x v="3"/>
-    <n v="559.91"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="57"/>
-    <x v="11"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="58"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="59"/>
-    <x v="11"/>
-    <n v="16.059999999999999"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="59"/>
-    <x v="13"/>
-    <n v="24.98"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="60"/>
-    <x v="29"/>
-    <n v="17.64"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="61"/>
-    <x v="11"/>
-    <n v="9.09"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="61"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="62"/>
-    <x v="30"/>
-    <n v="38.32"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="62"/>
-    <x v="31"/>
-    <n v="24.74"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="62"/>
-    <x v="32"/>
-    <n v="41.16"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="63"/>
-    <x v="11"/>
-    <n v="80.790000000000006"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="63"/>
-    <x v="23"/>
-    <n v="59.48"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="63"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="64"/>
-    <x v="3"/>
-    <n v="817.14"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="64"/>
-    <x v="3"/>
-    <n v="817.14"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="64"/>
-    <x v="11"/>
-    <n v="82.36"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="64"/>
-    <x v="6"/>
-    <n v="13.89"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="64"/>
-    <x v="1"/>
-    <n v="1247.44"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="65"/>
-    <x v="33"/>
-    <n v="6.41"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="66"/>
-    <x v="3"/>
-    <n v="363.08"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="66"/>
-    <x v="3"/>
-    <n v="363.08"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="66"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="67"/>
-    <x v="34"/>
-    <n v="4.58"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="67"/>
-    <x v="35"/>
-    <n v="9.76"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="68"/>
-    <x v="36"/>
-    <n v="22"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="69"/>
-    <x v="37"/>
-    <n v="6.48"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="69"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="69"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="70"/>
-    <x v="9"/>
-    <n v="89.52"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="71"/>
-    <x v="16"/>
-    <n v="7"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="71"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="72"/>
-    <x v="27"/>
-    <n v="37.979999999999997"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="72"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="72"/>
-    <x v="5"/>
-    <n v="10.66"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="73"/>
-    <x v="6"/>
-    <n v="11.61"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="73"/>
-    <x v="5"/>
-    <n v="41"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="74"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="74"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="75"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="76"/>
-    <x v="2"/>
-    <n v="24.22"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="77"/>
-    <x v="11"/>
-    <n v="4.32"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="77"/>
-    <x v="5"/>
-    <n v="35.15"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="78"/>
-    <x v="11"/>
-    <n v="21.32"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="79"/>
-    <x v="6"/>
-    <n v="42.7"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="80"/>
-    <x v="6"/>
-    <n v="224.7"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="80"/>
-    <x v="0"/>
-    <n v="41.34"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="81"/>
-    <x v="6"/>
-    <n v="210.79"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="81"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="82"/>
-    <x v="3"/>
-    <n v="769.72"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="82"/>
-    <x v="3"/>
-    <n v="1216.94"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="82"/>
-    <x v="3"/>
-    <n v="1216.94"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="83"/>
-    <x v="3"/>
-    <n v="769.72"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="83"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="84"/>
-    <x v="11"/>
-    <n v="22.98"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="85"/>
-    <x v="39"/>
-    <n v="39"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="85"/>
-    <x v="11"/>
-    <n v="51.05"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="85"/>
-    <x v="6"/>
-    <n v="68.47"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="86"/>
-    <x v="11"/>
-    <n v="5.09"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="87"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="88"/>
-    <x v="1"/>
-    <n v="1247.44"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="89"/>
-    <x v="0"/>
-    <n v="49.72"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="90"/>
-    <x v="11"/>
-    <n v="42.23"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="90"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="91"/>
-    <x v="21"/>
-    <n v="7.27"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="91"/>
-    <x v="13"/>
-    <n v="20.52"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="92"/>
-    <x v="6"/>
-    <n v="22.37"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="92"/>
-    <x v="0"/>
-    <n v="117.69"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="93"/>
-    <x v="3"/>
-    <n v="601.4"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="93"/>
-    <x v="3"/>
-    <n v="601.4"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="93"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="93"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="94"/>
-    <x v="9"/>
-    <n v="111.18"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="95"/>
-    <x v="11"/>
-    <n v="57.32"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="95"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="95"/>
-    <x v="40"/>
-    <n v="8000"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="96"/>
-    <x v="41"/>
-    <n v="27.77"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="96"/>
-    <x v="10"/>
-    <n v="33.299999999999997"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="96"/>
-    <x v="22"/>
-    <n v="78"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="97"/>
-    <x v="11"/>
-    <n v="67.63"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="98"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="99"/>
-    <x v="20"/>
-    <n v="29"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="99"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="100"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="100"/>
-    <x v="0"/>
-    <n v="6.41"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="101"/>
-    <x v="3"/>
-    <n v="207.08"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="101"/>
-    <x v="11"/>
-    <n v="31"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="101"/>
-    <x v="32"/>
-    <n v="23.26"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="102"/>
-    <x v="3"/>
-    <n v="283.07"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="102"/>
-    <x v="2"/>
-    <n v="26.04"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="102"/>
-    <x v="0"/>
-    <n v="32.5"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="103"/>
-    <x v="3"/>
-    <n v="283.07"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="104"/>
-    <x v="27"/>
-    <n v="39.44"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="105"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="105"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="106"/>
-    <x v="42"/>
-    <n v="9.6199999999999992"/>
-    <x v="0"/>
-    <x v="18"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="106"/>
-    <x v="11"/>
-    <n v="91.03"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="107"/>
-    <x v="42"/>
-    <n v="20"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="107"/>
-    <x v="42"/>
-    <n v="6.25"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="108"/>
-    <x v="27"/>
-    <n v="38.630000000000003"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="108"/>
-    <x v="11"/>
-    <n v="6.11"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="108"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="109"/>
-    <x v="3"/>
-    <n v="235.18"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="109"/>
-    <x v="3"/>
-    <n v="466.36"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="110"/>
-    <x v="43"/>
-    <n v="65.81"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="111"/>
-    <x v="3"/>
-    <n v="235.18"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="111"/>
-    <x v="11"/>
-    <n v="24.12"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="111"/>
-    <x v="1"/>
-    <n v="1247.44"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="111"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="112"/>
-    <x v="16"/>
-    <n v="4"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="113"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="113"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="114"/>
-    <x v="44"/>
-    <n v="16.18"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="114"/>
-    <x v="11"/>
-    <n v="9.56"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="114"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="115"/>
-    <x v="11"/>
-    <n v="46.01"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="116"/>
-    <x v="11"/>
-    <n v="12.55"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="116"/>
-    <x v="9"/>
-    <n v="89.46"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="117"/>
-    <x v="3"/>
-    <n v="283.44"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="117"/>
-    <x v="3"/>
-    <n v="283.44"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="117"/>
-    <x v="11"/>
-    <n v="7.02"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="118"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="119"/>
-    <x v="16"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="119"/>
-    <x v="13"/>
-    <n v="22.66"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="119"/>
-    <x v="11"/>
-    <n v="13.9"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="120"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="121"/>
-    <x v="10"/>
-    <n v="38.520000000000003"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="121"/>
-    <x v="11"/>
-    <n v="2.69"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="122"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="122"/>
-    <x v="3"/>
-    <n v="89.45"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="122"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="123"/>
-    <x v="3"/>
-    <n v="89.45"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="124"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="125"/>
-    <x v="18"/>
-    <n v="8.5"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="125"/>
-    <x v="0"/>
-    <n v="74.97"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="126"/>
-    <x v="3"/>
-    <n v="942.76"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="126"/>
-    <x v="3"/>
-    <n v="942.76"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="126"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="127"/>
-    <x v="11"/>
-    <n v="9.6199999999999992"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="128"/>
-    <x v="16"/>
-    <n v="3.5"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="128"/>
-    <x v="13"/>
-    <n v="22.66"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="129"/>
-    <x v="11"/>
-    <n v="7.57"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="130"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="131"/>
-    <x v="1"/>
-    <n v="1247.44"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="131"/>
-    <x v="42"/>
-    <n v="25"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="131"/>
-    <x v="5"/>
-    <n v="36.44"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="132"/>
-    <x v="27"/>
-    <n v="34.479999999999997"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="132"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="133"/>
-    <x v="11"/>
-    <n v="44.25"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="133"/>
-    <x v="0"/>
-    <n v="212.32"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="134"/>
-    <x v="33"/>
-    <n v="6.41"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="134"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="135"/>
-    <x v="3"/>
-    <n v="259.87"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="136"/>
-    <x v="3"/>
-    <n v="242.16"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="136"/>
-    <x v="3"/>
-    <n v="259.87"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="136"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="137"/>
-    <x v="3"/>
-    <n v="242.16"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="137"/>
-    <x v="11"/>
-    <n v="5.39"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="137"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="138"/>
-    <x v="9"/>
-    <n v="89.46"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="139"/>
-    <x v="45"/>
-    <n v="33.51"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="140"/>
-    <x v="46"/>
-    <n v="36.24"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="141"/>
-    <x v="47"/>
-    <n v="15.23"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="141"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="141"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="142"/>
-    <x v="48"/>
-    <n v="28.54"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="142"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="143"/>
-    <x v="3"/>
-    <n v="61.43"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="143"/>
-    <x v="3"/>
-    <n v="102.88"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="143"/>
-    <x v="3"/>
-    <n v="102.88"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="143"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="144"/>
-    <x v="11"/>
-    <n v="28.93"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="144"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="145"/>
-    <x v="3"/>
-    <n v="61.43"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="145"/>
-    <x v="16"/>
-    <n v="9.58"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="146"/>
-    <x v="5"/>
-    <n v="26.59"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="147"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="148"/>
-    <x v="49"/>
-    <n v="33.67"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="149"/>
-    <x v="11"/>
-    <n v="7.61"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="150"/>
-    <x v="5"/>
-    <n v="34.380000000000003"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="151"/>
-    <x v="23"/>
-    <n v="6.6"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="152"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="153"/>
-    <x v="3"/>
-    <n v="816.27"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="153"/>
-    <x v="10"/>
-    <n v="40.44"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="153"/>
-    <x v="1"/>
-    <n v="1247.44"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="154"/>
-    <x v="11"/>
-    <n v="6.27"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="154"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="155"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="156"/>
-    <x v="0"/>
-    <n v="76.47"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="157"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="157"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="158"/>
-    <x v="9"/>
-    <n v="89.4"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="159"/>
-    <x v="44"/>
-    <n v="13.67"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="159"/>
-    <x v="50"/>
-    <n v="33.659999999999997"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="160"/>
-    <x v="3"/>
-    <n v="269.56"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="160"/>
-    <x v="3"/>
-    <n v="159.38"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="160"/>
-    <x v="10"/>
-    <n v="41.07"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="160"/>
-    <x v="11"/>
-    <n v="5.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="160"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="161"/>
-    <x v="3"/>
-    <n v="269.56"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="161"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="162"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="162"/>
-    <x v="0"/>
-    <n v="14.98"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="163"/>
-    <x v="0"/>
-    <n v="23.47"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="164"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="165"/>
-    <x v="3"/>
-    <n v="34.18"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="165"/>
-    <x v="3"/>
-    <n v="99.76"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="165"/>
-    <x v="3"/>
-    <n v="99.76"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="166"/>
-    <x v="3"/>
-    <n v="34.18"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="167"/>
-    <x v="5"/>
-    <n v="42.31"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="168"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="169"/>
-    <x v="10"/>
-    <n v="35.65"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="170"/>
-    <x v="11"/>
-    <n v="11.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="170"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="171"/>
-    <x v="23"/>
-    <n v="47.4"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="171"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="172"/>
-    <x v="0"/>
-    <n v="109.83"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="173"/>
-    <x v="3"/>
-    <n v="687.29"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="173"/>
-    <x v="3"/>
-    <n v="687.29"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="173"/>
-    <x v="1"/>
-    <n v="1247.44"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="173"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="174"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="175"/>
-    <x v="23"/>
-    <n v="18"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="175"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="176"/>
-    <x v="27"/>
-    <n v="38.86"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="176"/>
-    <x v="11"/>
-    <n v="7.87"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="177"/>
-    <x v="11"/>
-    <n v="47.16"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="177"/>
-    <x v="9"/>
-    <n v="89.4"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="178"/>
-    <x v="11"/>
-    <n v="5.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="179"/>
-    <x v="3"/>
-    <n v="134.34"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="179"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="180"/>
-    <x v="11"/>
-    <n v="10.17"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="180"/>
-    <x v="11"/>
-    <n v="8.8000000000000007"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="180"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="181"/>
-    <x v="11"/>
-    <n v="4.32"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="181"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="182"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="182"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="183"/>
-    <x v="0"/>
-    <n v="47.38"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="184"/>
-    <x v="6"/>
-    <n v="69.400000000000006"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="184"/>
-    <x v="6"/>
-    <n v="6.83"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="185"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="185"/>
-    <x v="51"/>
-    <n v="48.64"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="186"/>
-    <x v="16"/>
-    <n v="5"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="186"/>
-    <x v="52"/>
-    <n v="38"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="187"/>
-    <x v="50"/>
-    <n v="40.71"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="188"/>
-    <x v="3"/>
-    <n v="128.12"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="188"/>
-    <x v="3"/>
-    <n v="284.95999999999998"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="188"/>
-    <x v="3"/>
-    <n v="284.95999999999998"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="188"/>
-    <x v="11"/>
-    <n v="13.36"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="188"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="189"/>
-    <x v="32"/>
-    <n v="23.26"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="189"/>
-    <x v="53"/>
-    <n v="46.7"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="190"/>
-    <x v="16"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="190"/>
-    <x v="3"/>
-    <n v="128.12"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="190"/>
-    <x v="11"/>
-    <n v="15.66"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="190"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="191"/>
-    <x v="3"/>
-    <n v="124.03"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="191"/>
-    <x v="3"/>
-    <n v="124.03"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="191"/>
-    <x v="1"/>
-    <n v="1209.18"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="192"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="193"/>
-    <x v="5"/>
-    <n v="27"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="194"/>
-    <x v="10"/>
-    <n v="38.06"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="194"/>
-    <x v="6"/>
-    <n v="80.650000000000006"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="194"/>
-    <x v="6"/>
-    <n v="31.2"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="195"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="195"/>
-    <x v="0"/>
-    <n v="19.98"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="195"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="196"/>
-    <x v="11"/>
-    <n v="53.68"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="197"/>
-    <x v="9"/>
-    <n v="89.4"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="198"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="199"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="200"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="201"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="201"/>
-    <x v="11"/>
-    <n v="33.549999999999997"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="201"/>
-    <x v="6"/>
-    <n v="45.24"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="201"/>
-    <x v="18"/>
-    <n v="8"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="202"/>
-    <x v="3"/>
-    <n v="544.37"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="203"/>
-    <x v="3"/>
-    <n v="353.83"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="203"/>
-    <x v="3"/>
-    <n v="353.83"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="203"/>
-    <x v="27"/>
-    <n v="34.659999999999997"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="204"/>
-    <x v="11"/>
-    <n v="7.57"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="205"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="205"/>
-    <x v="0"/>
-    <n v="29.98"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="206"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="207"/>
-    <x v="5"/>
-    <n v="25.4"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="208"/>
-    <x v="23"/>
-    <n v="12.71"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="208"/>
-    <x v="54"/>
-    <n v="14.75"/>
-    <x v="0"/>
-    <x v="19"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="208"/>
-    <x v="11"/>
-    <n v="92.49"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="208"/>
-    <x v="43"/>
-    <n v="54"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="209"/>
-    <x v="11"/>
-    <n v="5.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="210"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="211"/>
-    <x v="3"/>
-    <n v="262.51"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="211"/>
-    <x v="3"/>
-    <n v="262.51"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="211"/>
-    <x v="1"/>
-    <n v="1209.18"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="212"/>
-    <x v="13"/>
-    <n v="23.66"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="213"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="214"/>
-    <x v="10"/>
-    <n v="36.51"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="215"/>
-    <x v="0"/>
-    <n v="53.95"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="215"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="216"/>
-    <x v="11"/>
-    <n v="5.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="217"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="217"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="218"/>
-    <x v="23"/>
-    <n v="27"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="218"/>
-    <x v="44"/>
-    <n v="14.19"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="218"/>
-    <x v="55"/>
-    <n v="24.4"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="219"/>
-    <x v="11"/>
-    <n v="10.18"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="219"/>
-    <x v="5"/>
-    <n v="22.33"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="220"/>
-    <x v="11"/>
-    <n v="4.8"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="220"/>
-    <x v="11"/>
-    <n v="37.43"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="220"/>
-    <x v="11"/>
-    <n v="10.15"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="220"/>
-    <x v="9"/>
-    <n v="89.54"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="221"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="222"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="223"/>
-    <x v="23"/>
-    <n v="22.8"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="223"/>
-    <x v="6"/>
-    <n v="15.47"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="223"/>
-    <x v="6"/>
-    <n v="6.4"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="223"/>
-    <x v="32"/>
-    <n v="23.26"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="224"/>
-    <x v="23"/>
-    <n v="20"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="224"/>
-    <x v="39"/>
-    <n v="29.15"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="224"/>
-    <x v="6"/>
-    <n v="10.02"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="225"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="225"/>
-    <x v="3"/>
-    <n v="421.96"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="226"/>
-    <x v="11"/>
-    <n v="5.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="226"/>
-    <x v="6"/>
-    <n v="37.409999999999997"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="227"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="228"/>
-    <x v="5"/>
-    <n v="16.8"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="228"/>
-    <x v="17"/>
-    <n v="74.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="229"/>
-    <x v="42"/>
-    <n v="17"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="229"/>
-    <x v="5"/>
-    <n v="28.4"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="230"/>
-    <x v="3"/>
-    <n v="582.99"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="230"/>
-    <x v="3"/>
-    <n v="751.5"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="231"/>
-    <x v="3"/>
-    <n v="582.99"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="231"/>
-    <x v="11"/>
-    <n v="6.27"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="232"/>
-    <x v="11"/>
-    <n v="5.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="232"/>
-    <x v="18"/>
-    <n v="8"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="232"/>
-    <x v="0"/>
-    <n v="13.13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="233"/>
-    <x v="27"/>
-    <n v="30.03"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="233"/>
-    <x v="11"/>
-    <n v="148.15"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="233"/>
-    <x v="1"/>
-    <n v="1209.18"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="234"/>
-    <x v="16"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="234"/>
-    <x v="56"/>
-    <n v="20.65"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="234"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="235"/>
-    <x v="11"/>
-    <n v="21.38"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="235"/>
-    <x v="11"/>
-    <n v="13.48"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="235"/>
-    <x v="7"/>
-    <n v="40"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="236"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="236"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="237"/>
-    <x v="11"/>
-    <n v="12.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="238"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="239"/>
-    <x v="18"/>
-    <n v="10.29"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="240"/>
-    <x v="9"/>
-    <n v="89.54"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="241"/>
-    <x v="2"/>
-    <n v="27"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="242"/>
-    <x v="11"/>
-    <n v="21.39"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="242"/>
-    <x v="6"/>
-    <n v="17.100000000000001"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="242"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="243"/>
-    <x v="5"/>
-    <n v="63"/>
-    <x v="0"/>
-    <x v="19"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="243"/>
-    <x v="27"/>
-    <n v="20.010000000000002"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="243"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="244"/>
-    <x v="16"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="244"/>
-    <x v="3"/>
-    <n v="311.02"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="244"/>
-    <x v="3"/>
-    <n v="311.02"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="244"/>
-    <x v="22"/>
-    <n v="56.52"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="244"/>
-    <x v="0"/>
-    <n v="49.99"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="244"/>
-    <x v="0"/>
-    <n v="41.72"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="244"/>
-    <x v="0"/>
-    <n v="24.3"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="245"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="245"/>
-    <x v="0"/>
-    <n v="43.01"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="246"/>
-    <x v="3"/>
-    <n v="464.03"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="246"/>
-    <x v="10"/>
-    <n v="30.38"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="247"/>
-    <x v="3"/>
-    <n v="464.03"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="247"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="248"/>
-    <x v="57"/>
-    <n v="21.38"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="248"/>
-    <x v="6"/>
-    <n v="22.14"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="249"/>
-    <x v="6"/>
-    <n v="28"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="250"/>
-    <x v="6"/>
-    <n v="38.4"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="251"/>
-    <x v="44"/>
-    <n v="56.07"/>
-    <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="251"/>
-    <x v="10"/>
-    <n v="32.47"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="251"/>
-    <x v="10"/>
-    <n v="7.48"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="251"/>
-    <x v="17"/>
-    <n v="75.989999999999995"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="251"/>
-    <x v="0"/>
-    <n v="44.99"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="252"/>
-    <x v="23"/>
-    <n v="12"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="253"/>
-    <x v="23"/>
-    <n v="14"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="253"/>
-    <x v="3"/>
-    <n v="860.05"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="253"/>
-    <x v="11"/>
-    <n v="55.04"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="254"/>
-    <x v="0"/>
-    <n v="13.09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="255"/>
-    <x v="3"/>
-    <n v="499.6"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="256"/>
-    <x v="1"/>
-    <n v="1100"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="256"/>
-    <x v="0"/>
-    <n v="42.1"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="257"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="258"/>
-    <x v="5"/>
-    <n v="23.49"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="259"/>
-    <x v="7"/>
-    <n v="45"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="260"/>
-    <x v="3"/>
-    <n v="491.45"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="260"/>
-    <x v="3"/>
-    <n v="491.45"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="260"/>
-    <x v="3"/>
-    <n v="281.83999999999997"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="260"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="261"/>
-    <x v="11"/>
-    <n v="58.79"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="261"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="261"/>
-    <x v="9"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="262"/>
-    <x v="10"/>
-    <n v="28.92"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="263"/>
-    <x v="11"/>
-    <n v="6.06"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="264"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="264"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="265"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="265"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="266"/>
-    <x v="3"/>
-    <n v="277.99"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="267"/>
-    <x v="3"/>
-    <n v="277.99"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="268"/>
-    <x v="11"/>
-    <n v="21.06"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="268"/>
-    <x v="0"/>
-    <n v="11.7"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="268"/>
-    <x v="0"/>
-    <n v="4.21"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="269"/>
-    <x v="17"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="270"/>
-    <x v="3"/>
-    <n v="1900"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="270"/>
-    <x v="10"/>
-    <n v="31.32"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="271"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="271"/>
-    <x v="58"/>
-    <n v="9.4700000000000006"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="271"/>
-    <x v="0"/>
-    <n v="13.09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="272"/>
-    <x v="6"/>
-    <n v="86.97"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="272"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="20"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="273"/>
-    <x v="1"/>
-    <n v="1100"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="274"/>
-    <x v="7"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="275"/>
-    <x v="16"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="275"/>
-    <x v="2"/>
-    <n v="27.47"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="276"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="277"/>
-    <x v="16"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="277"/>
-    <x v="3"/>
-    <n v="133.94999999999999"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="277"/>
-    <x v="27"/>
-    <n v="24.01"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="278"/>
-    <x v="11"/>
-    <n v="30.54"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="278"/>
-    <x v="9"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="279"/>
-    <x v="11"/>
-    <n v="8.2100000000000009"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="280"/>
-    <x v="3"/>
-    <n v="207.47"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="280"/>
-    <x v="3"/>
-    <n v="207.47"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="280"/>
-    <x v="11"/>
-    <n v="4.59"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="280"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="280"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="281"/>
-    <x v="23"/>
-    <n v="8"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="281"/>
-    <x v="5"/>
-    <n v="32.75"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="281"/>
-    <x v="0"/>
-    <n v="37.450000000000003"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="282"/>
-    <x v="3"/>
-    <n v="574.84"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="282"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="283"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="283"/>
-    <x v="3"/>
-    <n v="292.54000000000002"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="283"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="284"/>
-    <x v="3"/>
-    <n v="292.54000000000002"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="284"/>
-    <x v="11"/>
-    <n v="46.96"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="285"/>
-    <x v="27"/>
-    <n v="33.799999999999997"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="285"/>
-    <x v="17"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="286"/>
-    <x v="58"/>
-    <n v="25.77"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="287"/>
-    <x v="11"/>
-    <n v="32.07"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="288"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="288"/>
-    <x v="0"/>
-    <n v="13.09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="289"/>
-    <x v="11"/>
-    <n v="92.04"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="289"/>
-    <x v="1"/>
-    <n v="1100"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="289"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="20"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="290"/>
-    <x v="22"/>
-    <n v="7"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="291"/>
-    <x v="3"/>
-    <n v="491.86"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="292"/>
-    <x v="27"/>
-    <n v="34.08"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="292"/>
-    <x v="0"/>
-    <n v="27.17"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="292"/>
-    <x v="7"/>
-    <n v="49"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="293"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="294"/>
-    <x v="9"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="294"/>
-    <x v="59"/>
-    <n v="3.02"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="295"/>
-    <x v="3"/>
-    <n v="532.86"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="295"/>
-    <x v="3"/>
-    <n v="301.79000000000002"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="296"/>
-    <x v="3"/>
-    <n v="305.27"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="296"/>
-    <x v="3"/>
-    <n v="301.79000000000002"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="296"/>
-    <x v="18"/>
-    <n v="8"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="297"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="297"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="298"/>
-    <x v="60"/>
-    <n v="320.99"/>
-    <x v="0"/>
-    <x v="21"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="298"/>
-    <x v="11"/>
-    <n v="16.23"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="299"/>
-    <x v="0"/>
-    <n v="13.84"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="299"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="300"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="301"/>
-    <x v="27"/>
-    <n v="37.51"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="302"/>
-    <x v="16"/>
-    <n v="5.2"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="303"/>
-    <x v="17"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="304"/>
-    <x v="0"/>
-    <n v="16.04"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="305"/>
-    <x v="23"/>
-    <n v="49.63"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="305"/>
-    <x v="11"/>
-    <n v="4.46"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="306"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="307"/>
-    <x v="16"/>
-    <n v="12.84"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="308"/>
-    <x v="3"/>
-    <n v="957.6"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="309"/>
-    <x v="3"/>
-    <n v="1552.65"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="309"/>
-    <x v="3"/>
-    <n v="600.51"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="309"/>
-    <x v="0"/>
-    <n v="13.09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="310"/>
-    <x v="1"/>
-    <n v="1100"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="311"/>
-    <x v="11"/>
-    <n v="5.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="311"/>
-    <x v="0"/>
-    <n v="35.9"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="311"/>
-    <x v="4"/>
-    <n v="11.76"/>
-    <x v="0"/>
-    <x v="20"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="312"/>
-    <x v="0"/>
-    <n v="27.54"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="313"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="314"/>
-    <x v="3"/>
-    <n v="436.75"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="314"/>
-    <x v="11"/>
-    <n v="10.7"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="314"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="314"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="315"/>
-    <x v="9"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="316"/>
-    <x v="60"/>
-    <n v="44.93"/>
-    <x v="0"/>
-    <x v="21"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="316"/>
-    <x v="11"/>
-    <n v="41.34"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="316"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="317"/>
-    <x v="39"/>
-    <n v="38.94"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="317"/>
-    <x v="11"/>
-    <n v="16.87"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="317"/>
-    <x v="61"/>
-    <n v="20.64"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="318"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="319"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="320"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="320"/>
-    <x v="3"/>
-    <n v="604.32000000000005"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="320"/>
-    <x v="3"/>
-    <n v="458.1"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="321"/>
-    <x v="3"/>
-    <n v="604.32000000000005"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="321"/>
-    <x v="11"/>
-    <n v="10.89"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="322"/>
-    <x v="23"/>
-    <n v="14.4"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="322"/>
-    <x v="32"/>
-    <n v="64.52"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="323"/>
-    <x v="6"/>
-    <n v="29.56"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="324"/>
-    <x v="17"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="325"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="326"/>
-    <x v="23"/>
-    <n v="40"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="326"/>
-    <x v="3"/>
-    <n v="268.95999999999998"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="326"/>
-    <x v="5"/>
-    <n v="14.74"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="327"/>
-    <x v="3"/>
-    <n v="268.95999999999998"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="327"/>
-    <x v="11"/>
-    <n v="5.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="328"/>
-    <x v="27"/>
-    <n v="39.08"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="329"/>
-    <x v="0"/>
-    <n v="13.09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="330"/>
-    <x v="1"/>
-    <n v="1100"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="331"/>
-    <x v="3"/>
-    <n v="758.07"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="332"/>
-    <x v="4"/>
-    <n v="13.9"/>
-    <x v="0"/>
-    <x v="20"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="333"/>
-    <x v="0"/>
-    <n v="16.940000000000001"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="334"/>
-    <x v="0"/>
-    <n v="38.56"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="335"/>
-    <x v="60"/>
-    <n v="331.69"/>
-    <x v="0"/>
-    <x v="21"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="335"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="335"/>
-    <x v="62"/>
-    <n v="3.2"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="335"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="336"/>
-    <x v="60"/>
-    <n v="21.39"/>
-    <x v="0"/>
-    <x v="21"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="336"/>
-    <x v="9"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="336"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="337"/>
-    <x v="3"/>
-    <n v="480.88"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="337"/>
-    <x v="39"/>
-    <n v="35.24"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="337"/>
-    <x v="22"/>
-    <n v="98.19"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="337"/>
-    <x v="32"/>
-    <n v="23.11"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="338"/>
-    <x v="11"/>
-    <n v="2.02"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="339"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="340"/>
-    <x v="3"/>
-    <n v="575.33000000000004"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="340"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="341"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="341"/>
-    <x v="3"/>
-    <n v="415.47"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="341"/>
-    <x v="5"/>
-    <n v="32.53"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="342"/>
-    <x v="3"/>
-    <n v="765.68"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="342"/>
-    <x v="6"/>
-    <n v="27.96"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="342"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="342"/>
-    <x v="18"/>
-    <n v="8"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="343"/>
-    <x v="39"/>
-    <n v="36.76"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="343"/>
-    <x v="6"/>
-    <n v="30.99"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="344"/>
-    <x v="24"/>
-    <n v="34.33"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="345"/>
-    <x v="3"/>
-    <n v="765.68"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="346"/>
-    <x v="17"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="346"/>
-    <x v="5"/>
-    <n v="34.82"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="347"/>
-    <x v="0"/>
-    <n v="13.09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="348"/>
-    <x v="16"/>
-    <n v="2.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="348"/>
-    <x v="3"/>
-    <n v="260.95"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="348"/>
-    <x v="1"/>
-    <n v="1100"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="349"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="349"/>
-    <x v="4"/>
-    <n v="13.9"/>
-    <x v="0"/>
-    <x v="20"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="350"/>
-    <x v="11"/>
-    <n v="23"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="350"/>
-    <x v="24"/>
-    <n v="23.24"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="351"/>
-    <x v="16"/>
-    <n v="3.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="351"/>
-    <x v="11"/>
-    <n v="5.64"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="352"/>
-    <x v="3"/>
-    <n v="458.56"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="352"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="352"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="353"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="354"/>
-    <x v="9"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="355"/>
-    <x v="3"/>
-    <n v="152.72"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="355"/>
-    <x v="3"/>
-    <n v="152.72"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="356"/>
-    <x v="11"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="357"/>
-    <x v="27"/>
-    <n v="33.159999999999997"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="358"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="358"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="359"/>
-    <x v="23"/>
-    <n v="15"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="359"/>
-    <x v="10"/>
-    <n v="41.83"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="360"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="361"/>
-    <x v="3"/>
-    <n v="375.26"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="361"/>
-    <x v="40"/>
-    <n v="9200"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="361"/>
-    <x v="3"/>
-    <n v="100.68"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="362"/>
-    <x v="3"/>
-    <n v="100.68"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="362"/>
-    <x v="12"/>
-    <n v="2000"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="363"/>
-    <x v="23"/>
-    <n v="15"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="364"/>
-    <x v="27"/>
-    <n v="30.64"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="365"/>
-    <x v="17"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="366"/>
-    <x v="16"/>
-    <n v="7"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="366"/>
-    <x v="11"/>
-    <n v="99.47"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="366"/>
-    <x v="63"/>
-    <n v="24.97"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="366"/>
-    <x v="2"/>
-    <n v="24"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="366"/>
-    <x v="0"/>
-    <n v="13.09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="367"/>
-    <x v="6"/>
-    <n v="229.9"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="367"/>
-    <x v="1"/>
-    <n v="1100"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="368"/>
-    <x v="4"/>
-    <n v="13.9"/>
-    <x v="0"/>
-    <x v="20"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="369"/>
-    <x v="23"/>
-    <n v="19"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="369"/>
-    <x v="12"/>
-    <n v="2250"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="370"/>
-    <x v="3"/>
-    <n v="220.08"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="370"/>
-    <x v="11"/>
-    <n v="92.98"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="370"/>
-    <x v="32"/>
-    <n v="23.26"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="371"/>
-    <x v="6"/>
-    <n v="103.14"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="372"/>
-    <x v="3"/>
-    <n v="305.27999999999997"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="372"/>
-    <x v="3"/>
-    <n v="220.08"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="373"/>
-    <x v="3"/>
-    <n v="549.72"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="373"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="374"/>
-    <x v="9"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="374"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="375"/>
-    <x v="11"/>
-    <n v="87.14"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="376"/>
-    <x v="0"/>
-    <n v="89.99"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="376"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="377"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="378"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="378"/>
-    <x v="3"/>
-    <n v="814.5"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="378"/>
-    <x v="27"/>
-    <n v="36.42"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="378"/>
-    <x v="11"/>
-    <n v="29.83"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="378"/>
-    <x v="18"/>
-    <n v="8.82"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="379"/>
-    <x v="3"/>
-    <n v="115.52"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="379"/>
-    <x v="12"/>
-    <n v="2250"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="379"/>
-    <x v="24"/>
-    <n v="28"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="380"/>
-    <x v="3"/>
-    <n v="257.08"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="380"/>
-    <x v="2"/>
-    <n v="26.67"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="381"/>
-    <x v="3"/>
-    <n v="257.08"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="382"/>
-    <x v="16"/>
-    <n v="2.5"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="383"/>
-    <x v="20"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="384"/>
-    <x v="6"/>
-    <n v="44.31"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="385"/>
-    <x v="11"/>
-    <n v="5.35"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="385"/>
-    <x v="22"/>
-    <n v="44.92"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="386"/>
-    <x v="11"/>
-    <n v="15.77"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="386"/>
-    <x v="17"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="387"/>
-    <x v="0"/>
-    <n v="13.09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="388"/>
-    <x v="1"/>
-    <n v="1100"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="388"/>
-    <x v="12"/>
-    <n v="2250"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="389"/>
-    <x v="27"/>
-    <n v="36.36"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="389"/>
-    <x v="11"/>
-    <n v="3.96"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="389"/>
-    <x v="5"/>
-    <n v="23.47"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="390"/>
-    <x v="4"/>
-    <n v="13.9"/>
-    <x v="0"/>
-    <x v="20"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="391"/>
-    <x v="23"/>
-    <n v="18"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="391"/>
-    <x v="3"/>
-    <n v="349.28"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="391"/>
-    <x v="3"/>
-    <n v="117.65"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="392"/>
-    <x v="3"/>
-    <n v="521.16999999999996"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="392"/>
-    <x v="3"/>
-    <n v="117.65"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="392"/>
-    <x v="6"/>
-    <n v="125"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="393"/>
-    <x v="11"/>
-    <n v="11.72"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="394"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="394"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="395"/>
-    <x v="9"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="395"/>
-    <x v="2"/>
-    <n v="26.67"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="396"/>
-    <x v="16"/>
-    <n v="2.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="397"/>
-    <x v="3"/>
-    <n v="335.2"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="397"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="398"/>
-    <x v="12"/>
-    <n v="2250"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="398"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="399"/>
-    <x v="3"/>
-    <n v="87.17"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="399"/>
-    <x v="11"/>
-    <n v="33.15"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="399"/>
-    <x v="20"/>
-    <n v="19"/>
-    <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="399"/>
-    <x v="5"/>
-    <n v="3.5"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="400"/>
-    <x v="3"/>
-    <n v="1248.95"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="401"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="401"/>
-    <x v="16"/>
-    <n v="2.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="402"/>
-    <x v="10"/>
-    <n v="34.69"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="403"/>
-    <x v="16"/>
-    <n v="2.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="404"/>
-    <x v="18"/>
-    <n v="39.43"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="405"/>
-    <x v="6"/>
-    <n v="66.75"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="406"/>
-    <x v="16"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="407"/>
-    <x v="16"/>
-    <n v="2.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="407"/>
-    <x v="17"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="407"/>
-    <x v="12"/>
-    <n v="2250"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="408"/>
-    <x v="6"/>
-    <n v="68.040000000000006"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="408"/>
-    <x v="26"/>
-    <n v="41.78"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="409"/>
-    <x v="0"/>
-    <n v="13.09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="410"/>
-    <x v="1"/>
-    <n v="1100"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="410"/>
-    <x v="22"/>
-    <n v="41.24"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="411"/>
-    <x v="4"/>
-    <n v="13.9"/>
-    <x v="0"/>
-    <x v="20"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="412"/>
-    <x v="16"/>
-    <n v="3.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="413"/>
-    <x v="3"/>
-    <n v="1390.37"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="413"/>
-    <x v="3"/>
-    <n v="1390.37"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="413"/>
-    <x v="3"/>
-    <n v="502.75"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="414"/>
-    <x v="23"/>
-    <n v="12.87"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="415"/>
-    <x v="23"/>
-    <n v="19.3"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="416"/>
-    <x v="10"/>
-    <n v="28.77"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="416"/>
-    <x v="11"/>
-    <n v="65.09"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="416"/>
-    <x v="6"/>
-    <n v="26.25"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="416"/>
-    <x v="8"/>
-    <n v="10.69"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="416"/>
-    <x v="7"/>
-    <n v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="417"/>
-    <x v="3"/>
-    <n v="360.56"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="417"/>
-    <x v="9"/>
-    <n v="65"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="418"/>
-    <x v="3"/>
-    <n v="360.56"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="419"/>
-    <x v="16"/>
-    <n v="2.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="419"/>
-    <x v="12"/>
-    <n v="2250"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="420"/>
-    <x v="11"/>
-    <n v="46.44"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="421"/>
-    <x v="0"/>
-    <n v="47.66"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="422"/>
-    <x v="3"/>
-    <n v="90.57"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="422"/>
-    <x v="3"/>
-    <n v="90.57"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="422"/>
-    <x v="14"/>
-    <n v="35"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="423"/>
-    <x v="3"/>
-    <n v="186.13"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="423"/>
-    <x v="15"/>
-    <n v="60"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="424"/>
-    <x v="38"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="424"/>
-    <x v="3"/>
-    <n v="1606.46"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="425"/>
-    <x v="23"/>
-    <n v="40.81"/>
-    <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="425"/>
-    <x v="16"/>
-    <n v="2.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="426"/>
-    <x v="3"/>
-    <n v="9.43"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="427"/>
-    <x v="54"/>
-    <n v="131.1"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="428"/>
-    <x v="3"/>
-    <n v="9.43"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="428"/>
-    <x v="11"/>
-    <n v="27.71"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="428"/>
-    <x v="0"/>
-    <n v="24.63"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="429"/>
-    <x v="12"/>
-    <n v="2250"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="430"/>
-    <x v="27"/>
-    <n v="33.46"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="430"/>
-    <x v="64"/>
-    <n v="4.2699999999999996"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="431"/>
-    <x v="16"/>
-    <n v="1.75"/>
-    <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="431"/>
-    <x v="17"/>
-    <n v="75"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8BC6F50E-3369-4C90-9799-7EC7CD832CF2}" name="TablaDinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField numFmtId="164" showAll="0">
-      <items count="433">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item x="368"/>
-        <item x="369"/>
-        <item x="370"/>
-        <item x="371"/>
-        <item x="372"/>
-        <item x="373"/>
-        <item x="374"/>
-        <item x="375"/>
-        <item x="376"/>
-        <item x="377"/>
-        <item x="378"/>
-        <item x="379"/>
-        <item x="380"/>
-        <item x="381"/>
-        <item x="382"/>
-        <item x="383"/>
-        <item x="384"/>
-        <item x="385"/>
-        <item x="386"/>
-        <item x="387"/>
-        <item x="388"/>
-        <item x="389"/>
-        <item x="390"/>
-        <item x="391"/>
-        <item x="392"/>
-        <item x="393"/>
-        <item x="394"/>
-        <item x="395"/>
-        <item x="396"/>
-        <item x="397"/>
-        <item x="398"/>
-        <item x="399"/>
-        <item x="400"/>
-        <item x="401"/>
-        <item x="402"/>
-        <item x="403"/>
-        <item x="404"/>
-        <item x="405"/>
-        <item x="406"/>
-        <item x="407"/>
-        <item x="408"/>
-        <item x="409"/>
-        <item x="410"/>
-        <item x="411"/>
-        <item x="412"/>
-        <item x="413"/>
-        <item x="414"/>
-        <item x="415"/>
-        <item x="416"/>
-        <item x="417"/>
-        <item x="418"/>
-        <item x="419"/>
-        <item x="420"/>
-        <item x="421"/>
-        <item x="422"/>
-        <item x="423"/>
-        <item x="424"/>
-        <item x="425"/>
-        <item x="426"/>
-        <item x="427"/>
-        <item x="428"/>
-        <item x="429"/>
-        <item x="430"/>
-        <item x="431"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="33"/>
-        <item x="5"/>
-        <item x="59"/>
-        <item x="20"/>
-        <item x="26"/>
-        <item x="30"/>
-        <item x="60"/>
-        <item x="12"/>
-        <item x="37"/>
-        <item x="21"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="18"/>
-        <item x="34"/>
-        <item x="44"/>
-        <item x="31"/>
-        <item x="46"/>
-        <item x="14"/>
-        <item x="49"/>
-        <item x="3"/>
-        <item x="52"/>
-        <item x="22"/>
-        <item x="55"/>
-        <item x="7"/>
-        <item x="25"/>
-        <item x="53"/>
-        <item x="45"/>
-        <item x="32"/>
-        <item x="11"/>
-        <item x="6"/>
-        <item x="63"/>
-        <item x="17"/>
-        <item x="36"/>
-        <item x="48"/>
-        <item x="43"/>
-        <item x="19"/>
-        <item x="56"/>
-        <item x="41"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="40"/>
-        <item x="1"/>
-        <item x="42"/>
-        <item x="4"/>
-        <item x="57"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="15"/>
-        <item x="39"/>
-        <item x="58"/>
-        <item x="54"/>
-        <item x="64"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="16"/>
-        <item x="38"/>
-        <item x="29"/>
-        <item x="51"/>
-        <item x="62"/>
-        <item x="2"/>
-        <item x="35"/>
-        <item x="50"/>
-        <item x="61"/>
-        <item x="47"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="23">
-        <item x="16"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="3"/>
-        <item x="21"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="19"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="15"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="8"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="20"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="23">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de Amount" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8459,212 +694,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB4A22C-70B6-4B2B-A01D-577349A79BAF}">
-  <dimension ref="A3:B26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="5">
-        <v>539.13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="5">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="5">
-        <v>115.54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5">
-        <v>63561.119999999966</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="5">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="5">
-        <v>9.6199999999999992</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="5">
-        <v>330.63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="5">
-        <v>77.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="5">
-        <v>1715.17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="5">
-        <v>2795.21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="5">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15" s="5">
-        <v>19092.87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="5">
-        <v>1570.88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="5">
-        <v>1680.3999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="5">
-        <v>24754.500000000004</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="5">
-        <v>222.18999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="5">
-        <v>224.48999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="5">
-        <v>93750</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="5">
-        <v>2613.02</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="5">
-        <v>1973.24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="5">
-        <v>104.78000000000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="5">
-        <v>2776</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="5">
-        <v>220353.53999999995</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K807"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8717,18 +746,8 @@
       <c r="F2" t="s">
         <v>94</v>
       </c>
-      <c r="H2">
-        <f>COUNTBLANK(A2:A807)</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <f>MIN(A2:A807)</f>
-        <v>43101</v>
-      </c>
-      <c r="K2" s="2">
-        <f>MAX(A2:A807)</f>
-        <v>43738</v>
-      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
@@ -8749,10 +768,6 @@
       <c r="F3" t="s">
         <v>95</v>
       </c>
-      <c r="H3">
-        <f>COUNTBLANK(B2:B807)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
@@ -8773,18 +788,6 @@
       <c r="F4" t="s">
         <v>96</v>
       </c>
-      <c r="H4">
-        <f>COUNTBLANK(C2:C807)</f>
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <f>MIN(C2:C807)</f>
-        <v>1.75</v>
-      </c>
-      <c r="K4">
-        <f>MAX(C2:C807)</f>
-        <v>9200</v>
-      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
@@ -8805,10 +808,6 @@
       <c r="F5" t="s">
         <v>94</v>
       </c>
-      <c r="H5">
-        <f>COUNTBLANK(D2:D807)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
@@ -8829,10 +828,6 @@
       <c r="F6" t="s">
         <v>94</v>
       </c>
-      <c r="H6">
-        <f>COUNTBLANK(E2:E807)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
@@ -8852,10 +847,6 @@
       </c>
       <c r="F7" t="s">
         <v>96</v>
-      </c>
-      <c r="H7">
-        <f>COUNTBLANK(F2:F807)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
